--- a/data/sxbet/ligas/Leagues Cup/trades.xlsx
+++ b/data/sxbet/ligas/Leagues Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x848837022989ee9dec208574f5d50ab7affffe028314c6870f307c31bef629f9</t>
+          <t>0x5dd37dc23cbce86ed38247f14fffc57361dad217bb4abbcd12cadceb44ad80f6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5975</t>
+          <t>1.6913</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Minnesota United</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Leagues Cup</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Minnesota United vs FC Juarez</t>
+          <t>Vancouver Whitecaps vs Atlante</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xa947ef8257fa77bf9bf63b430cdba1a0674915e675f85052f9b34c137885a429</t>
+          <t>0x3ded5e2e1bf81a8e54f161a5067d4fac7dff64b7e0885aec08f7b4af7dfcc439</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19648563</t>
+          <t>L19648601</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785876313</t>
+          <t>1785898547</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785889800</t>
+          <t>1785897000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.67364</t>
+          <t>1.44664</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,39 +635,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x58e408a89e1b9a79d32f656842d9e8ebb23fce40e148acfdc0d6860341fc7787</t>
+          <t>0x7ee6b44d9dd42a7af98699b88963c06a3b962055c339309bebac33e51b5f48a8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>87.94432</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Charlotte FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Leagues Cup</t>
@@ -683,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Charlotte FC vs Pumas UNAM</t>
+          <t>Vancouver Whitecaps vs Atlante</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Charlotte FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x5d152e8ce49fc8cc655b57972fcffe2ee3358f987e1bab480ecc2f00fbf498bb</t>
+          <t>0x2a72a32e89615e68d175f5ffb33956eb0a72dc0f7b7136213207c74a8e05a01f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19648524</t>
+          <t>L19648601</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785876305</t>
+          <t>1785898477</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785888000</t>
+          <t>1785897000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.985112</t>
+          <t>177.665293</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,19 +739,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9f5bef4ebeb1af959a717da66cd39c462d25e1d23012d5a95ddd3b9997883e25</t>
+          <t>0xcf267373adae008324ff0c6c0fbc072c943e4d4fcdd1b6d45a724abbd75e3190</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>1</t>
@@ -775,19 +755,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5225</t>
+          <t>1.6637</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>FC Cincinnati</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Leagues Cup</t>
@@ -795,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FC Cincinnati vs C.F. Pachuca</t>
+          <t>Vancouver Whitecaps vs Atlante</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C.F. Pachuca</t>
+          <t>Atlante</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd3e1c653b21c1a64cb64c9084561b673d57dbfc63f670529e4145012a37fe4cf</t>
+          <t>0x3ded5e2e1bf81a8e54f161a5067d4fac7dff64b7e0885aec08f7b4af7dfcc439</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19636566</t>
+          <t>L19648601</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785876297</t>
+          <t>1785898311</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785887100</t>
+          <t>1785897000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.913876</t>
+          <t>1.506591</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,27 +843,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x06db3661bf475c8e25aac9229739925c9fb7bc2ad41371e835d73e14341a4c86</t>
+          <t>0x87cbe05968d16734ea0b1fb406aa4497d109d6f2fd146a7b2ccf220a008e97bf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>1.67997</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.845</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -895,26 +867,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Vancouver Whitecaps</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Leagues Cup</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps vs Atlante</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Atlante</t>
@@ -922,7 +890,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xcd9aaa7185a9f5b48f0732c0b7c8b38f3c793cacf15333860d9e633479dfa629</t>
+          <t>0x3a1fb66aaf2b22287926d646a240daf0f66531085cf9abbd5827ed128ef5cf42</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785876281</t>
+          <t>1785898256</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.232641</t>
+          <t>1.98813</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,110 +947,9062 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>0x266b2802bc0071fa00ed2faf91277cd535d81aee914700929a9d348c5463e7f2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.07999</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x2de765bc2f0fd65361900207e5c91f3f6bf1ab06335d1f7314075784dbfbb53b</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1785898234</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3.40982</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0xca48480cfa9d153326dc1eda8671520b005d52c32cf3bcfdb66f08d2b0337bc6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20.19</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0xd0df5e751bd11dbbb5199772c7853b1989cb783ce2a516dd81a034080b2730ed</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785898096</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>33.098361</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0xc7335acfa16506a5aeab90c3f161144b89a69a11dd6e33e0374d1eeaebc91921</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>265.32</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.6088</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0xd0df5e751bd11dbbb5199772c7853b1989cb783ce2a516dd81a034080b2730ed</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785898080</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>435.843943</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0x465118fbae3b170f4044524aebcf736058afdedfc3de6c6e01169a9851c4851b</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>51.67</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.3075</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x43b145da7b9598172a9ef73f53cb3eacd4927803175af89ec19bd49dd5d1528f</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19648524</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785897728</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785888000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>168.03252</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0xa4783b31824af6bc3d0368810c383482e5f9ffb2488d03690f5d4a9862cedae2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0x129181d6059542cab1fcecdefc7e98f5386c0512b95c4ccec1c21f6e8a1c0646</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19648524</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785897567</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785888000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>25.423423</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0xfe6d7ceb5ecacde2c2e246a5df058f2ad216b0068983d59d88c64cd3d98a0437</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>26.01</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.3113</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xcd9ea1cca63a73a5df87d5ddde6d6023344a5e1c4960caa2380c692ffeb7541f</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785897384</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>83.566265</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x241097454018f9cd49e36d61c31abb8229d60f869fa680f4d7b4f9f5e8f4b1b7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x31eed84E4EEAaA6c20EB2b3D5Dc80Ad13dBCB13b</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.8625</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.7312</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x372c30bcfa6fc1d0944dd3aa5cae1b2275441c0ade8696ecc56860009fd383cf</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785897010</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>5.282051</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0xb7a2a31918ffcd6c860370e693eeeb4d6932f7d0592ff54aaeabf0f2b9411c08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xfc21e68ab7c8e20de27672221ace77039937a58c24c79f5aa9aa0c5642446ef1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785896288</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>11.627907</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x662aaecb3b97da6e7753a45707eb2b99b9080eba7a8c53382efa41a346d19f86</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0xfc21e68ab7c8e20de27672221ace77039937a58c24c79f5aa9aa0c5642446ef1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785896286</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>11.627907</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x1ff363bf7056f17cf59c6eaf6f03975c4e7f015ca40425687336a1c8237a9e91</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>37.50052</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0xfc21e68ab7c8e20de27672221ace77039937a58c24c79f5aa9aa0c5642446ef1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785896260</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>87.210512</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x584e4deded14644bc5d86f8c7e608a1ba0a81ea245ac407ce562e005f37f6e03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16.24947</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0xfc21e68ab7c8e20de27672221ace77039937a58c24c79f5aa9aa0c5642446ef1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785896257</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>37.789465</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0x5eff1f4b029bff941cb78d1369c9c8ee45ace293588a5c15cefd4467e4432f00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>64.375</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.1287</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x3a1fb66aaf2b22287926d646a240daf0f66531085cf9abbd5827ed128ef5cf42</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785895639</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0xb4cccd173990a8e9295b01f12a86622098ad16e77b1f71bdfbfe762b79d98816</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>13.37069</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.1287</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x3a1fb66aaf2b22287926d646a240daf0f66531085cf9abbd5827ed128ef5cf42</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785895594</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>103.850019</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x14122bc249b488e74865277fadbd401bc538bdf77a695a691317b941b525a1b3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>149.27</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.3313</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x5d152e8ce49fc8cc655b57972fcffe2ee3358f987e1bab480ecc2f00fbf498bb</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19648524</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785895168</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785888000</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>450.626415</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x4f01afce5bf6e5d74e36f43e4094fe3a06cc11634b9a4f15bf5d11b73268f453</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0xbaebe21454b82dc283402f842b24d9e4da914f7d75b70695c15664d8b63228d6</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785895004</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>38.461538</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0xdd5595a4e425022f63fd6be5e81c5742e04035c765a3d2870168b28cc0183068</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>121.72745</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.4387</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x3ded5e2e1bf81a8e54f161a5067d4fac7dff64b7e0885aec08f7b4af7dfcc439</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785894493</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>277.441481</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0xa8226cbf58079bcf408c50c1966db0f1dc672e6d1e62c27f82cd0283314bebe6</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>34.62</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.4387</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x3ded5e2e1bf81a8e54f161a5067d4fac7dff64b7e0885aec08f7b4af7dfcc439</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785894493</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>78.905983</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x29c1166ce5e0a91f3a4fc70425407168725ee0ff909b8f72037d8dba9c48c34e</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>206.08999</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps -1.5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0xd0df5e751bd11dbbb5199772c7853b1989cb783ce2a516dd81a034080b2730ed</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785894397</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>406.08865</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0xe6dba3e54a6b2f28b86c35ff62529ea6565b8293742e4a3343d20bdfb1d86eba</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>47.38</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.505</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps -1.5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0xd0df5e751bd11dbbb5199772c7853b1989cb783ce2a516dd81a034080b2730ed</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785894362</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>93.821782</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x9da952d097f54a7f6417965844ae236dbff51a17f83094c2e47dae5a245ba7c0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>43.77</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.505</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps -1.5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0xd0df5e751bd11dbbb5199772c7853b1989cb783ce2a516dd81a034080b2730ed</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785894361</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>86.673267</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0x9ae4528c2acaf85035cdf8d006a7241b25a26e6aae22876c3810505620703805</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>58.94</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.505</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps -1.5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xd0df5e751bd11dbbb5199772c7853b1989cb783ce2a516dd81a034080b2730ed</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785894360</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>116.712871</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x677426ae2e2f1d1f5255dd1f85db11d6b7241b241a4681bfb320e939bd9feeb8</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>53.95</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.505</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps -1.5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xd0df5e751bd11dbbb5199772c7853b1989cb783ce2a516dd81a034080b2730ed</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785894359</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>106.831683</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0x9753eacccbe17d493e41fef3dde22cea734a7b60a32fa2c1b6ac0d1fc35b288d</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.80772</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.6812</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xd96305c31746dfab2a8709d2af7dd52ec104fe34b8ae57dbc9a37743c0f5d14d</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785894129</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2.653534</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0x6c1d953afc75371ff69530a4e31da9247b9af733daa357da0fc2c9f237ddcee7</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>156.70768</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.4275</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0xcc4dd3259d144191a5cea63ca7e9d6ba6ba9acd07b660820b4bce5ebc3a0f54d</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785893824</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>366.567673</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x6bcfa97cb1a808c6ddb8782aa703ec4fc472a77bc84b79ec66a24f62361be73f</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>48.66406</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.4275</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785893823</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>113.834058</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x44da3009a23cec875a406a1ad0f86139e10541e817d1ac1bc505f64ae0a6f88c</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>48.66406</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.4275</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0xcc4dd3259d144191a5cea63ca7e9d6ba6ba9acd07b660820b4bce5ebc3a0f54d</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785893823</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>113.834058</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xb0ac0a2b5d10e649b5d6f48c09473f998244a213ecd29eec4da087e3c72983d9</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4.99999</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.5787</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x08650e47fef50081dc0b738a75a79ba71c7f0e8609175dad57f432d9e06b3ef8</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785893737</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>8.639292</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x79ccd2c65748911bf2a0e94ba93ddbab87f433c40834d92f1001c31cabcbd620</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0xcc4dd3259d144191a5cea63ca7e9d6ba6ba9acd07b660820b4bce5ebc3a0f54d</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785893735</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>11.363636</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x643f3aab607fd07e37514ee2b78a6f1b2c636cb230c0c2cf99f2386d137150bb</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>185.02138</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.5787</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x08650e47fef50081dc0b738a75a79ba71c7f0e8609175dad57f432d9e06b3ef8</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785893727</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>319.691369</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x114a44dff257c78d8309e237e150b1c7875f86abea8fbee070987f62211db0c1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>25.80999</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.5463</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0xcc4dd3259d144191a5cea63ca7e9d6ba6ba9acd07b660820b4bce5ebc3a0f54d</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785893714</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>47.24941</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0xbaf816e41f54e76411e7308821b4277d69cc1f00d09b5c124016fdf05316d3a2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>121.42</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.5288</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tigres UANL 0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785893629</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>229.635934</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x95f1c06a129e263c2e9b99c4d773cf39c219503adf24179ce4b8d57dc0868864</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x31eed84E4EEAaA6c20EB2b3D5Dc80Ad13dBCB13b</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1.43125</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.2862</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x43b145da7b9598172a9ef73f53cb3eacd4927803175af89ec19bd49dd5d1528f</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19648524</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785893575</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785888000</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0xaa21e1e80c1901b6b8aae0255bd04aa6edc89ba6c67d1a88f300789b355a24d0</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>81.39</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.5288</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tigres UANL 0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785893572</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>153.929078</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x1ca6a35fce42d8017edefb8c2aa0169de351cdf545223acae26ce54b7bb62913</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.5212</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tigres UANL 0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785893466</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>37.77458</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0xe39cde5817c744bb2fd0e92ca0ced656f5df4dabd076f2743839ac16cccede61</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.24999</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.5188</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tigres UANL 0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785893428</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2.409619</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x293eb7b80b8b5c7d6a7b612575fc0470ad58490c53eafd55ff0cfefdec1c1c4c</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>188.29</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.2087</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0xf6e78d648c45fe65c9c7f3364643a1527c1982204b28b2764ad1544002b6b33a</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19648524</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785893160</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785888000</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>901.988024</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x7b30b4a9127767624169556b4130fff3c3d492fe907264556e432c3ba234c067</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x51F8e5692A80d7752047bc43Ab5444953F542F91</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2.83998</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.7488</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0xcd9ea1cca63a73a5df87d5ddde6d6023344a5e1c4960caa2380c692ffeb7541f</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785893121</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>3.792962</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0xaf8f207d338470fda5a6a968b45a7567a99f51787b32be2dbc9cb85ada41e5e7</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785892044</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>5.81393</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0xb976e21c904063086ec07b0f63d33c46cb5258cf7fa6acf04d753578d068cf93</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785892042</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>5.81393</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x1bf0363f0519ea01f063361f62c0bc24ab3617706f6dd2ff1a4024e8afcc67c0</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785892040</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>5.81393</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0xdd1356f9ca166d9ecb9a65d7faba19199532afaa4b4f56ab19917d1d47d1174d</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785892039</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5.81393</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0xc9225abedbbe5f079fb4818ca9510ce8a61af49f8d07db0b9c4572007bafe153</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785892037</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>5.81393</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x1c5b479b5183ef5d843c0181e15f707c7e1580d328538c2bd5e2faa0376c0904</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785892035</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>5.81393</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x84ff50b2b5307d59eef6df4bbc1c40016c6c66bb897c39c806afa971d81ec88d</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>71.87137</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785892007</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>83.57136</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x9413defb5e929e6d93d04e60b2a3d3a2dbf0c65e7df7e93aed6cbc912199f600</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>23.40423</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785892006</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>27.214221</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0x75c3724b242102fd4da1a890a39e77fdbf710d30782fb4e7405935e34f9769b1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>102.58566</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785892004</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>119.285651</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x89a7fb1cd036258a2a387010cc151822b50e3c11b718bbccf057abe5596f929f</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>13.82137</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785892002</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>16.07136</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0xcf5b0b8cc4e96d23249c016098535b15101f50d456d056cd657eadaaa02d4461</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785892001</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>5.81393</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x2109f33a306ea30babfc4fbe90d811c23cad01a57bd7a5cdd63f7b007de23ee7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>36.85709</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1785892001</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>42.857081</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0xfc96025103e2c78dd06692309e8d64c938fe35fc9353cb7d062a1bd01b5e71ca</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1785891999</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>5.81393</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x784b4003d555fd2b78fb336dadf2c46bd39333725f161cc59086c3c8e43ecc2b</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>16.83137</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785891999</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>19.57136</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0x409b0cc2af2580121d6668246eaa535fd7f41ad97f1df0a3ff1bfc06d94d74bf</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>30.59137</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1785891974</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>35.57136</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x80246b0141d1cd003514ae2cbbc7d4931f0d845c1756b8735b8ada38e9af43dc</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>31.9428</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0x1c905ccf0eb10c4b39d5e0bc84449050baf5eaa6505f97896dcdcfc554cd0081</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1785891973</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>37.142791</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0xa72ce6aef025c17d8d82d727b84486737906aa087c996d454293ae633e8e0192</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>202.01</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.5025</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1785890152</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>402.00995</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x6f2ac0f8993790a123e270b3bce08eb1087d30fb3c90555f99c7ce1c735b1d8c</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>19.5558</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.5888</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x571377dea32549c6162fa02f539f4b99e1b3094e9f127ff05e9d946b1c27662e</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1785889922</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>33.215796</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0xecfb279066085e0d132eb183f7184c8b6ba9ee24c99af23613c3568f5240a085</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.515</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1785889851</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>9.708738</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x17a5bd038c5bda97f902c574ea0049e2a8d296f033f9630c707926ee61cad0ad</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>51.09649</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.515</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1785889823</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>99.216485</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0xbf6932b4f60f712be185aff2016265e94db60de02daca442850c52ec9a15cd03</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.515</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1785889456</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>9.708738</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x5a8577fdce787d1652494b9da305498465aa4ae8dbe3b343517374398d571a8b</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>15.23762</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.515</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1785889432</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>29.587612</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0xe3d70b68ee34a0291090ac5b50a7a44e28451a7d16210bcf638d926cdae472a6</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.515</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1785889355</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>9.708738</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x3d9d6d570452bb1f7780de3e8a67624b5cb8f662ece01214af4997aeac8ca3d0</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>14.29257</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.515</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1785889344</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>27.752563</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0xefc3aa0a5c447cfb172fb045fc35516f314eeff1fae5901def0bfe40b1eb5caf</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.515</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1785889321</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>9.708738</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x74bdd66630e3927fe555d5e44611383188ceda97af40f0c81caedfbbe5cb8d50</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>14.18639</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.515</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1785889317</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>27.546388</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x70e694e6bbb4f22b6417633f5643a1d87cfe2de36b370a2805d677c66ac41d5e</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>258.84847</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.6412</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x359fe5304ba684adf0d8e8dcc7ec17172d4716ba252d1ac053f29895713c1ad4</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1785889272</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>403.662331</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x7e7870cc29c8ba53b3d3733ab15a998c1a0c7073f6ca2838825235d70d225945</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>9.27</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.6412</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0x359fe5304ba684adf0d8e8dcc7ec17172d4716ba252d1ac053f29895713c1ad4</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1785889265</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>14.45614</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x67a15f76b440441a5734db1111684e34d95f9dfa6250c9bea0a8f8effcfb0a13</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>26.49</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.515</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1785889242</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>51.436893</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0xf1328dad7a48cb13e49f92a7fd3aa2cb5b0fcb31d103e1012e8186bd91d4bf20</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>59.9</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.5175</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0x1f9a71638421cb65353b385f77ff8b22154ac41d548687f3fec6d15d89400dbd</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19648578</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1785889143</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1785895200</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>115.748792</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x9abe848bf94f6f638138036f678009b4993625f533ffd1f63c02c8246be8f989</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>39.25842</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.585</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0x571377dea32549c6162fa02f539f4b99e1b3094e9f127ff05e9d946b1c27662e</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1785887450</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>67.10841</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0x16894bd8959f5751293cf9c58ffd73204f6e119171e6c8feaf15b200812a336b</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>32.58</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.4363</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x8faadda487289b319dddc2037df213b844e4a7663ddf40d76f15f64d2d265761</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19648524</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1785887067</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1785888000</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>74.681948</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0x3f36cddad3eaead1b511b914cd2afd957dbb5c57ff97509cd6d4721ff444f37f</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>26.53999</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.5525</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0x26449123c32874dbbbeed3a976b98e9426935c2920d94651e89b2954e5677f9e</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19648524</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1785886857</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1785888000</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>48.036181</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xd77b0e915b155f747a31e95658ab782540f81575fd16cb5b0aa8788f0fce5c17</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>13.70162</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.105</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0x27403e9c394935861443b4952968da5c48f783985f23c0e322848beaa99e86e0</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1785886388</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>130.491619</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0x02a74002c43eab0e34ecc7f49384fff3d8bc1f685fa4ddf91cfeb3b436363159</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>23.72599</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.6713</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0xb86e2b886d73eb8b9d190316a49914f7baa5846d66f3f0646a82f862f2b73f6b</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1785886387</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>35.345981</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0xd82c028b0535366eae59e372f5eef10ed45b15ee6902012b8908c91db5f27f0d</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.34396</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.0987</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0x3a1fb66aaf2b22287926d646a240daf0f66531085cf9abbd5827ed128ef5cf42</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1785886094</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>13.609722</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0x5a330ddaa8f74ee9334cfa97bd77fbe7ad722dbf620d31fa45eef09fe52fe1a5</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>10.2766</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x26449123c32874dbbbeed3a976b98e9426935c2920d94651e89b2954e5677f9e</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19648524</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1785884471</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1785888000</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>19.389811</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0x620dc6e7d673fdc8a36bbf2bfa95c14ad360c725c09bfaeba42b5680c365b945</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x26449123c32874dbbbeed3a976b98e9426935c2920d94651e89b2954e5677f9e</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19648524</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1785884466</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1785888000</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1.886792</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0xf99933fc2b7305ff08f53676fec9a1685b962b86d79261f24db7de4254ea02d4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.6713</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0xb86e2b886d73eb8b9d190316a49914f7baa5846d66f3f0646a82f862f2b73f6b</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1785884190</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>7.44876</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0xba22dd50e2017ba6cb78f04260dbfc9d7701a76448835e185718293cc0e47587</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>26.1966</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.6713</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0xb86e2b886d73eb8b9d190316a49914f7baa5846d66f3f0646a82f862f2b73f6b</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1785884156</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>39.026592</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0xfafbe0256ebbe386e46f2b4d43726c573c81e10561d24ec53cece9bdb8ea00df</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>13.04908</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0x571377dea32549c6162fa02f539f4b99e1b3094e9f127ff05e9d946b1c27662e</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1785884155</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>22.498414</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0xbc7f1ae1a58deb53250396fa382144e6526b45f027ac77e6fafac74fac18c1e6</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4.99999</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0x571377dea32549c6162fa02f539f4b99e1b3094e9f127ff05e9d946b1c27662e</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1785884155</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>8.620672</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0x1da97e121359a52c8f6779a5dad07eaf48d42466f107a7e1918e202c26567871</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>19.09856</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0x571377dea32549c6162fa02f539f4b99e1b3094e9f127ff05e9d946b1c27662e</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1785884133</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>32.928552</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0x848837022989ee9dec208574f5d50ab7affffe028314c6870f307c31bef629f9</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.5975</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Minnesota United vs FC Juarez</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0xa947ef8257fa77bf9bf63b430cdba1a0674915e675f85052f9b34c137885a429</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19648563</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1785876313</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1785889800</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1.67364</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0x58e408a89e1b9a79d32f656842d9e8ebb23fce40e148acfdc0d6860341fc7787</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.5038</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0x5d152e8ce49fc8cc655b57972fcffe2ee3358f987e1bab480ecc2f00fbf498bb</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19648524</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1785876305</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1785888000</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1.985112</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0x9f5bef4ebeb1af959a717da66cd39c462d25e1d23012d5a95ddd3b9997883e25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.5225</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>FC Cincinnati vs C.F. Pachuca</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>C.F. Pachuca</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0xd3e1c653b21c1a64cb64c9084561b673d57dbfc63f670529e4145012a37fe4cf</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19636566</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1785876297</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1785887100</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1.913876</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0x06db3661bf475c8e25aac9229739925c9fb7bc2ad41371e835d73e14341a4c86</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0.99998</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.8113</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Atlante</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Atlante</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0xcd9aaa7185a9f5b48f0732c0b7c8b38f3c793cacf15333860d9e633479dfa629</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19648601</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1785876281</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1785897000</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1.232641</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>0x7fdee12b66509b4e55d9cd06d636d596bc1c82783a54364f8a433918b68a3771</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
         <is>
           <t>1.585</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Columbus Crew</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Leagues Cup</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Leagues Cup</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
         <is>
           <t>Columbus Crew vs Atlas Guadalajara</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>Columbus Crew</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>Atlas Guadalajara</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>0x18e582b1c740328d239c7711491cd712723bf483eeb586f32123be8dd5d44234</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>L19636567</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
         <is>
           <t>1785876267</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>1785887100</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>1.709402</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V90" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
